--- a/overview.xlsx
+++ b/overview.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t xml:space="preserve">Market</t>
   </si>
@@ -62,6 +62,18 @@
   </si>
   <si>
     <t xml:space="preserve">ELMES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREV: book is not realistic (zero for many properties, book is low end of management estimate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">before div1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">after div1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Managmeent low</t>
   </si>
 </sst>
 </file>
@@ -75,7 +87,7 @@
     <numFmt numFmtId="167" formatCode="\$#,##0.0000"/>
     <numFmt numFmtId="168" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -118,8 +130,15 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -130,6 +149,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFB3CAC7"/>
         <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8CB"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -167,7 +192,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -196,6 +221,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -204,7 +233,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -253,7 +298,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFDDE8CB"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -334,9 +379,6 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="63">
-          <cell r="E63">
-            <v>3.97226698485198</v>
-          </cell>
           <cell r="F63">
             <v>26.2250710238931</v>
           </cell>
@@ -489,12 +531,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B5:I16"/>
+  <dimension ref="B5:I23"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="5.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.18"/>
   </cols>
   <sheetData>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -574,9 +619,8 @@
         <f aca="false">[3]Sheet1!G63</f>
         <v>29.4752287671436</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <f aca="false">[3]Sheet1!E63</f>
-        <v>3.97226698485198</v>
+      <c r="G8" s="7" t="n">
+        <v>21.24</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>46294</v>
@@ -592,35 +636,35 @@
       <c r="C9" s="2" t="n">
         <v>0.0431</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E9" s="8" t="n">
         <f aca="false">'[4]Investment case'!B24</f>
         <v>0</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="8" t="n">
         <f aca="false">'[4]Investment case'!D24</f>
         <v>0.2</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="8" t="n">
         <f aca="false">'[4]Investment case'!C24</f>
         <v>0.146788142364364</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0"/>
+      <c r="H9" s="1" t="n">
+        <v>2025</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="9" t="n">
         <f aca="false">E6/$C6-1</f>
         <v>0.551832952697505</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="9" t="n">
         <f aca="false">F6/$C6-1</f>
         <v>0.803066473364455</v>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="G13" s="10" t="n">
         <f aca="false">G6/$C6-1</f>
         <v>0.635675919809802</v>
       </c>
@@ -629,15 +673,15 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="11" t="n">
         <f aca="false">E7/$C7-1</f>
         <v>-1</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="11" t="n">
         <f aca="false">F7/$C7-1</f>
         <v>-1</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="10" t="n">
         <f aca="false">G7/$C7-1</f>
         <v>1.14565427961819</v>
       </c>
@@ -646,34 +690,70 @@
       <c r="B15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="9" t="n">
         <f aca="false">E8/$C8-1</f>
         <v>0.406170028090783</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="9" t="n">
         <f aca="false">F8/$C8-1</f>
         <v>0.58044122075837</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="10" t="n">
         <f aca="false">G8/$C8-1</f>
-        <v>-0.787009813144666</v>
+        <v>0.13887399463807</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="11" t="n">
         <f aca="false">E9/$C9-1</f>
         <v>-1</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="9" t="n">
         <f aca="false">F9/$C9-1</f>
         <v>3.64037122969838</v>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="G16" s="9" t="n">
         <f aca="false">G9/$C9-1</f>
         <v>2.40575736344232</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="0" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <f aca="false">F22-3.2</f>
+        <v>21.24</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C23" s="14"/>
+      <c r="F23" s="1" t="n">
+        <v>30.03</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <f aca="false">F23-3.2</f>
+        <v>26.83</v>
       </c>
     </row>
   </sheetData>
